--- a/medical_surveys_questionnaires/036_viral_infection_assessment_survey--medical_surveys_questionnaires.xlsx
+++ b/medical_surveys_questionnaires/036_viral_infection_assessment_survey--medical_surveys_questionnaires.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -951,8 +951,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -980,12 +980,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'family_member'}</t>
+          <t>family_member</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Family Member'}</t>
+          <t>Family Member</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'healthcare_worker'}</t>
+          <t>healthcare_worker</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Healthcare Worker'}</t>
+          <t>Healthcare Worker</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'public_place'}</t>
+          <t>public_place</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Public Place'}</t>
+          <t>Public Place</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'school/work'}</t>
+          <t>school/work</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'School/Work'}</t>
+          <t>School/Work</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'vaccinated'}</t>
+          <t>vaccinated</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Vaccinated'}</t>
+          <t>Vaccinated</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'previously_infected'}</t>
+          <t>previously_infected</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Previously Infected'}</t>
+          <t>Previously Infected</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'negative'}</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Negative'}</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'positive'}</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Positive'}</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'antibiotics'}</t>
+          <t>antibiotics</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Antibiotics'}</t>
+          <t>Antibiotics</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'antiviral'}</t>
+          <t>antiviral</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Antiviral'}</t>
+          <t>Antiviral</t>
         </is>
       </c>
     </row>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'antimalarial'}</t>
+          <t>antimalarial</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Antimalarial'}</t>
+          <t>Antimalarial</t>
         </is>
       </c>
     </row>
@@ -1218,12 +1218,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'antifungal'}</t>
+          <t>antifungal</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Antifungal'}</t>
+          <t>Antifungal</t>
         </is>
       </c>
     </row>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'allergies'}</t>
+          <t>allergies</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Allergies'}</t>
+          <t>Allergies</t>
         </is>
       </c>
     </row>
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'chronic_conditions'}</t>
+          <t>chronic_conditions</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Chronic Conditions'}</t>
+          <t>Chronic Conditions</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'hospital'}</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Hospital'}</t>
+          <t>Hospital</t>
         </is>
       </c>
     </row>
@@ -1320,12 +1320,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'clinic'}</t>
+          <t>clinic</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Clinic'}</t>
+          <t>Clinic</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'doctor'}</t>
+          <t>doctor</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Doctor'}</t>
+          <t>Doctor</t>
         </is>
       </c>
     </row>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'urgent_care'}</t>
+          <t>urgent_care</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Urgent Care'}</t>
+          <t>Urgent Care</t>
         </is>
       </c>
     </row>
@@ -1371,12 +1371,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'doctor'}</t>
+          <t>doctor</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Doctor'}</t>
+          <t>Doctor</t>
         </is>
       </c>
     </row>
@@ -1405,12 +1405,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'np'}</t>
+          <t>np</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'NP'}</t>
+          <t>NP</t>
         </is>
       </c>
     </row>
@@ -1422,12 +1422,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'pa'}</t>
+          <t>pa</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'PA'}</t>
+          <t>PA</t>
         </is>
       </c>
     </row>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'rn'}</t>
+          <t>rn</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'RN'}</t>
+          <t>RN</t>
         </is>
       </c>
     </row>
